--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
   <si>
     <t/>
   </si>
   <si>
-    <t>20064413</t>
-  </si>
-  <si>
-    <t>ATTACK JAZ CN 1.5 KG</t>
+    <t>20113567</t>
+  </si>
+  <si>
+    <t>GNTLE GEN M.B 700 ML</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -28,19 +28,25 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20113567</t>
-  </si>
-  <si>
-    <t>GNTLE GEN M.B 700 ML</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20115959</t>
+  </si>
+  <si>
+    <t>GENTLE GEN FP 700 ML</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
+    <t>20141372</t>
+  </si>
+  <si>
+    <t>GENTLE GEN LI 700 ML</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>10003272</t>
@@ -49,7 +55,7 @@
     <t>BAYGON SPR CT 675 ML</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
   </si>
   <si>
     <t>RT,(E-3.5B)</t>
@@ -445,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -511,15 +517,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -528,10 +534,30 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -16,10 +16,10 @@
     <t/>
   </si>
   <si>
-    <t>20113567</t>
-  </si>
-  <si>
-    <t>GNTLE GEN M.B 700 ML</t>
+    <t>10005803</t>
+  </si>
+  <si>
+    <t>SOKLN PWG RED 780 ML</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -31,34 +31,34 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20115959</t>
-  </si>
-  <si>
-    <t>GENTLE GEN FP 700 ML</t>
+    <t>10007389</t>
+  </si>
+  <si>
+    <t>SOKLN PWG PNK 780 ML</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20141372</t>
-  </si>
-  <si>
-    <t>GENTLE GEN LI 700 ML</t>
+    <t>10005482</t>
+  </si>
+  <si>
+    <t>SNLGHT LME PCH 660 G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>10003272</t>
-  </si>
-  <si>
-    <t>BAYGON SPR CT 675 ML</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20090067</t>
+  </si>
+  <si>
+    <t>SNLGHT M A.BAU 600 G</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
   </si>
 </sst>
 </file>
@@ -457,7 +457,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -537,15 +537,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -554,10 +554,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
